--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.24736320219878</v>
+        <v>8.002696520357302</v>
       </c>
       <c r="D2" t="n">
-        <v>48.18336723274353</v>
+        <v>7.829797175320824</v>
       </c>
       <c r="E2" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F2" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.64202029572743</v>
+        <v>5.629328298055708</v>
       </c>
       <c r="D3" t="n">
-        <v>33.71781095827448</v>
+        <v>5.479144280719603</v>
       </c>
       <c r="E3" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F3" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.02377942597745</v>
+        <v>3.091364156721335</v>
       </c>
       <c r="D4" t="n">
-        <v>19.73477257254939</v>
+        <v>3.206900543039275</v>
       </c>
       <c r="E4" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F4" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.25124000272892</v>
+        <v>1.990826500443449</v>
       </c>
       <c r="D5" t="n">
-        <v>13.2182394919428</v>
+        <v>2.147963917440705</v>
       </c>
       <c r="E5" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F5" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.34279462903301</v>
+        <v>1.355704127217864</v>
       </c>
       <c r="D6" t="n">
-        <v>47.12276134996503</v>
+        <v>7.657448719369317</v>
       </c>
       <c r="E6" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F6" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.74551187802565</v>
+        <v>7.596145680179169</v>
       </c>
       <c r="D7" t="n">
-        <v>46.7072631478138</v>
+        <v>7.589930261519743</v>
       </c>
       <c r="E7" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F7" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.15938259348724</v>
+        <v>4.413399671441677</v>
       </c>
       <c r="D8" t="n">
-        <v>27.11735532464246</v>
+        <v>4.4065702402544</v>
       </c>
       <c r="E8" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F8" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.43205096944641</v>
+        <v>3.645208282535041</v>
       </c>
       <c r="D9" t="n">
-        <v>22.25114605502613</v>
+        <v>3.615811233941745</v>
       </c>
       <c r="E9" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F9" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.33444579973372</v>
+        <v>6.06684744245673</v>
       </c>
       <c r="D10" t="n">
-        <v>37.2294034921113</v>
+        <v>6.049778067468087</v>
       </c>
       <c r="E10" t="n">
-        <v>13.65374841222085</v>
+        <v>2.218734116985888</v>
       </c>
       <c r="F10" t="n">
-        <v>12.26276647104848</v>
+        <v>1.992699551545378</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
